--- a/downloads/model-selection-tool.xlsx
+++ b/downloads/model-selection-tool.xlsx
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>Says "I donâ€™t know". When an input was missing, it said so instead of filling the gap.</t>
+          <t>Says "I don’t know". When an input was missing, it said so instead of filling the gap.</t>
         </is>
       </c>
       <c r="C38" s="21" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>The slowest 1 in 20 calls on a real long input breaks the workflowâ€™s time limit.</t>
+          <t>The slowest 1 in 20 calls on a real long input breaks the workflow’s time limit.</t>
         </is>
       </c>
       <c r="D46" s="21" t="inlineStr">
@@ -2740,7 +2740,7 @@
     <row r="17">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>Score what the runs showed, not what the card promises. A benchmark number is a claim about somebody elseâ€™s work. A blank row is a 0: if you did not run the case, you do not know.</t>
+          <t>Score what the runs showed, not what the card promises. A benchmark number is a claim about somebody else’s work. A blank row is a 0: if you did not run the case, you do not know.</t>
         </is>
       </c>
       <c r="B17" s="1" t="n"/>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>Says "I donâ€™t know". When an input was missing, it said so instead of filling the gap.</t>
+          <t>Says "I don’t know". When an input was missing, it said so instead of filling the gap.</t>
         </is>
       </c>
       <c r="C38" s="21" t="inlineStr">
@@ -5408,7 +5408,7 @@
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>The slowest 1 in 20 calls on a real long input breaks the workflowâ€™s time limit.</t>
+          <t>The slowest 1 in 20 calls on a real long input breaks the workflow’s time limit.</t>
         </is>
       </c>
       <c r="D46" s="21" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>Says "I donâ€™t know". When an input was missing, it said so instead of filling the gap.</t>
+          <t>Says "I don’t know". When an input was missing, it said so instead of filling the gap.</t>
         </is>
       </c>
       <c r="C38" s="21" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>The slowest 1 in 20 calls on a real long input breaks the workflowâ€™s time limit.</t>
+          <t>The slowest 1 in 20 calls on a real long input breaks the workflow’s time limit.</t>
         </is>
       </c>
       <c r="D46" s="21" t="inlineStr">

--- a/downloads/model-selection-tool.xlsx
+++ b/downloads/model-selection-tool.xlsx
@@ -126,7 +126,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -196,8 +196,26 @@
       <color rgb="00183D32"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Source Serif 4"/>
+      <b val="1"/>
+      <color rgb="00F5F0E6"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Figtree"/>
+      <color rgb="00F5F0E6"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Figtree"/>
+      <b val="1"/>
+      <color rgb="00F5F0E6"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -226,6 +244,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E5EBE1"/>
         <bgColor rgb="00E5EBE1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00183D32"/>
+        <bgColor rgb="00183D32"/>
       </patternFill>
     </fill>
   </fills>
@@ -298,7 +322,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -369,6 +393,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2962,7 +2995,11 @@
       <c r="F36" s="1" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n"/>
+      <c r="A37" s="27" t="inlineStr">
+        <is>
+          <t>The Living Craft cohort</t>
+        </is>
+      </c>
       <c r="B37" s="1" t="n"/>
       <c r="C37" s="1" t="n"/>
       <c r="D37" s="1" t="n"/>
@@ -2970,7 +3007,11 @@
       <c r="F37" s="1" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n"/>
+      <c r="A38" s="28" t="inlineStr">
+        <is>
+          <t>Choose against evidence from the work, not a fluent demonstration. Explore The Living Craft’s October 2026 cohort: 30 live hours with Sunil Mathew, plus independent work.</t>
+        </is>
+      </c>
       <c r="B38" s="1" t="n"/>
       <c r="C38" s="1" t="n"/>
       <c r="D38" s="1" t="n"/>
@@ -2978,7 +3019,11 @@
       <c r="F38" s="1" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n"/>
+      <c r="A39" s="29" t="inlineStr">
+        <is>
+          <t>Apply at https://learning.thelivingcraft.ai/#apply</t>
+        </is>
+      </c>
       <c r="B39" s="1" t="n"/>
       <c r="C39" s="1" t="n"/>
       <c r="D39" s="1" t="n"/>
@@ -4275,10 +4320,13 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId1"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>
 
